--- a/7-17事前指導_教室割当.xlsx
+++ b/7-17事前指導_教室割当.xlsx
@@ -10,20 +10,20 @@
     <sheet name="7-17教室割当一覧" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="教員8_詳細" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="教員16_詳細" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="教員5_詳細" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="教員11_詳細" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="教員2_詳細" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="教員10_詳細" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="教員4_詳細" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="教員9_詳細" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="教員6_詳細" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="教員3_詳細" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="教員7_詳細" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="教員15_詳細" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="教員12_詳細" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="教員13_詳細" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="教員14_詳細" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="教員1_詳細" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="教員2_詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="教員5_詳細" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="教員6_詳細" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="教員3_詳細" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="教員7_詳細" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="教員15_詳細" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="教員4_詳細" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="教員13_詳細" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="教員10_詳細" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="教員9_詳細" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="教員11_詳細" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="教員1_詳細" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="教員12_詳細" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="教員14_詳細" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,22 +743,22 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>7/31(金): 福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社 → 東名化学工業株式会社　小牧工場
+          <t>7/31(金): 江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園
 8/25(火): 株式会社青山製作所　大口工場 → 株式会社東海理化電機製作所 → 江南郵便局</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-3-8　2-3-13　2-3-10　2-4-13　2-1-34　2-1-35　2-4-29　2-1-7　2-2-3　2-2-5</t>
+          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25　2-3-10　2-4-13　2-1-34　2-1-35　2-4-29　2-1-7　2-2-3　2-2-5</t>
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
           <t>計
-20名</t>
+21名</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>教員5</t>
+          <t>教員2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
@@ -807,440 +807,440 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
+          <t>7/27(月): 株式会社青山製作所　大口工場 → 大口屋木賀工場
+7/28(火): サンハウス食品株式会社 → 江南市立草井保育園 → 株式会社扶桑守口食品</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>1-5-17　2-1-11　1-5-20　1-5-21　1-5-16　1-5-19　1-5-12　1-5-14　1-5-7　1-5-15</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>計
+16名</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>教員5</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
           <t>7/29(水): 株式会社青山製作所　大口工場 → キムラユニティー株式会社　犬山工場
-7/31(金): グンゼ江南工場 → 江南市立宮田東保育園</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2-2-14　2-4-21　2-1-1　2-1-19　2-4-14　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+7/30(木): 江南市立藤里保育園</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>2-2-14　2-4-21　2-1-1　2-1-19　2-4-14　2-4-7</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>教室3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>教員6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>7/29(水): 株式会社綿半ホームエイド江南店 → 江南市立藤里保育園
+7/30(木): 江南市立古知野中保育園 → 江南市立古知野西保育園 → ガレ・ドゥ・ワタナベ</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2-1-21　2-2-4　2-2-20　1-5-18　1-5-39　2-4-3　1-5-2　1-5-32　1-5-33　1-5-38</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>計
+17名</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>教員3</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>7/27(月): ドコモショップ江南店 → 江南市立藤里保育園 → GARN（ガルン）　モゾワンダーシティ店
+7/28(火): 江南中央食品 → 大口屋木賀工場</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>2-1-6　2-1-13　2-1-36　2-4-1　1-5-8　1-5-29　1-5-37</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>教室4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>教員7</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>7/29(水): 榮美容室本店
+7/30(木): 江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>1-5-27　1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>計
 18名</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>教員11</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr">
+    <row r="10" ht="50" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>教員15</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>7/31(金): 江南市立古知野東保育園
-8/24(月): きもの館なかね → 江南市立門弟山保育園 → 江南市立古知野西保育園</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>2-4-22　2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>教室3</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>教員2</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>8/26(水): 株式会社デンケン
+8/27(木): 株式会社林商店 → 江南市立宮田保育園 → 株式会社デンケン</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>2-1-25　2-4-28　2-4-15　2-4-19　2-1-30　2-2-19　2-3-14　2-4-16</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>教室5</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>教員4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>7/27(月): 株式会社青山製作所　大口工場 → 大口屋木賀工場
-7/28(火): サンハウス食品株式会社 → 江南市立草井保育園 → 株式会社扶桑守口食品</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>1-5-17　2-1-11　1-5-20　1-5-21　1-5-16　1-5-19　1-5-12　1-5-14　1-5-7　1-5-15</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>7/29(水): 江南中央食品 → 江南市立布袋西保育園 → ガレ・ドゥ・ワタナベ
+7/30(木): ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13　2-2-9　2-2-11　2-2-15　2-4-12</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>計
 17名</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+    <row r="12" ht="50" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>教員13</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>8/25(火): 江南市立宮田南保育園 → 江南市立宮田東保育園
+8/26(水): 株式会社愛知イエローハット　一宮店 → サロンド榮 → 九品寺幼稚園</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>2-1-18　2-4-6　2-1-2　2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>教室6</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>教員10</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>7/31(金): 東罐興業株式会社　小牧工場
-8/24(月): 美容室ISA → 江南市立古知野東保育園 → 江南市立小鹿保育園</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>1-5-34　2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>教室4</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>教員4</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>7/29(水): 江南中央食品 → 江南市立布袋西保育園 → ガレ・ドゥ・ワタナベ
-7/30(木): 江南市立藤里保育園 → ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13　2-4-7　2-2-9　2-2-11　2-2-15　2-4-12</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>7/31(金): 江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園
+8/24(月): きもの館なかね → 江南市立門弟山保育園 → 江南市立古知野西保育園</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>1-5-28　1-5-23　2-1-17　1-5-5　2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>計
 17名</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
+    <row r="14" ht="50" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>教員9</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>7/31(金): 江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>7/31(金): 福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社
 8/24(月): 福玉米粒麦株式会社 → 江南市立布袋保育園</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>1-5-28　1-5-23　2-1-17　1-5-5　2-1-22　2-2-1　2-2-12</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>教室5</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>教員6</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-1-22　2-2-1　2-2-12</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>教室7</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>教員11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>7/29(水): 株式会社綿半ホームエイド江南店 → 江南市立藤里保育園
-7/30(木): 江南市立古知野中保育園 → 江南市立古知野西保育園 → ガレ・ドゥ・ワタナベ</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>2-1-21　2-2-4　2-2-20　1-5-18　1-5-39　2-4-3　1-5-2　1-5-32　1-5-33　1-5-38</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>7/31(金): 東罐興業株式会社　小牧工場 → 東名化学工業株式会社　小牧工場
+8/24(月): 美容室ISA → 江南市立古知野東保育園 → 江南市立小鹿保育園</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>1-5-34　2-3-8　2-3-13　2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>計
 17名</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>教員3</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>教員1</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>7/27(月): ドコモショップ江南店 → 江南市立藤里保育園 → GARN（ガルン）　モゾワンダーシティ店
-7/28(火): 江南中央食品 → 大口屋木賀工場</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>2-1-6　2-1-13　2-1-36　2-4-1　1-5-8　1-5-29　1-5-37</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>教室6</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>教員7</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>7/27(月): きもの館なかね → 江南市立宮田南保育園 → 株式会社扶桑守口食品
+7/28(火): 江南市立藤里保育園 → 東名化学工業株式会社　小牧工場</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>1-5-9　1-5-10　1-5-26　1-5-30　1-5-40　2-2-13　2-1-15　2-4-20</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>教室8</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>教員12</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>7/29(水): 榮美容室本店
-7/30(木): 江南市立古知野東保育園 → 江南市立小鹿保育園 → リスパック株式会社 真空成形工場</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>1-5-27　1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>8/25(火): 株式会社愛知イエローハット　一宮店 → TJ天気予報 7mm 北名古屋店
+8/26(水): アメーテールアーム → アイカテック建材株式会社名古屋工場</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>2-2-2　2-2-18　2-1-10　2-1-31　2-1-12　2-4-10　2-3-5　2-3-19　2-4-17</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>計
 18名</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>教員15</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
+    <row r="18" ht="50" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>教員14</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>8/26(水): 株式会社デンケン
-8/27(木): 株式会社林商店 → 江南市立宮田保育園 → 株式会社デンケン</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>2-1-25　2-4-28　2-4-15　2-4-19　2-1-30　2-2-19　2-3-14　2-4-16</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>教室7</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>教員12</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>8/25(火): 株式会社愛知イエローハット　一宮店 → TJ天気予報 7mm 北名古屋店
-8/26(水): アメーテールアーム → アイカテック建材株式会社名古屋工場</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2-2-2　2-2-18　2-1-10　2-1-31　2-1-12　2-4-10　2-3-5　2-3-19　2-4-17</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>計
-17名</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>教員13</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>8/25(火): 江南市立宮田南保育園 → 江南市立宮田東保育園
-8/26(水): 株式会社愛知イエローハット　一宮店 → サロンド榮 → 九品寺幼稚園</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>2-1-18　2-4-6　2-1-2　2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>教室8</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>教員14</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>8/26(水): 株式会社綿半ホームエイド江南店 → 江南市立布袋東保育園
 8/27(木): 江南市立布袋東保育園 → 株式会社愛知イエローハット　一宮店 → FUSION</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>2-1-9　2-1-20　2-1-24　2-2-10　2-3-6　2-4-23　2-2-16　2-3-7　2-2-17</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G18" s="15" t="n">
         <v>9</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>計
-17名</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>教員1</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>7/27(月): きもの館なかね → 江南市立宮田南保育園 → 株式会社扶桑守口食品
-7/28(火): 江南市立藤里保育園 → 東名化学工業株式会社　小牧工場</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>1-5-9　1-5-10　1-5-26　1-5-30　1-5-40　2-2-13　2-1-15　2-4-20</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1303,7 +1303,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室5で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計9名（教室5で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -1338,74 +1338,69 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>株式会社綿半ホームエイド江南店
-江南市上奈良町緑13</t>
+          <t>江南中央食品
+江南市古知野町北屋敷242</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-1-21　2-2-4　2-2-20</t>
+          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>8.6km</t>
+          <t>7.7km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立藤里保育園
-江南市藤が丘7丁目1-16</t>
+          <t>江南市立布袋西保育園
+江南市木賀町定和３１</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>7/30(木)</t>
-        </is>
-      </c>
       <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>江南市立古知野中保育園
-江南市古知野町熱田203</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>1-5-18　1-5-39　2-4-3　1-5-2　1-5-32　1-5-33　1-5-38</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>9.7km</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>江南市立古知野西保育園
-江南市東野町郷前48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ガレ・ドゥ・ワタナベ
 江南市小折町八反畑8</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>7/30(木)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店
+愛知県名古屋市中村区並木1-81-1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2-2-9　2-2-11　2-2-15　2-4-12</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>40.6km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -1416,23 +1411,17 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -1477,7 +1466,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計7名（教室5で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計8名（教室5で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -1507,70 +1496,70 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>7/27(月)</t>
+          <t>8/25(火)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ドコモショップ江南店
-愛知県江南市木賀町定和163</t>
+          <t>江南市立宮田南保育園
+江南市前飛保町西町　2</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-1-6　2-1-13　2-1-36　2-4-1</t>
+          <t>2-1-18　2-4-6　2-1-2</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>32.1km</t>
+          <t>9.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立藤里保育園
-江南市藤が丘7丁目1-16</t>
+          <t>江南市立宮田東保育園
+江南市宮田神明町栄174</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
+      </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>GARN（ガルン）　モゾワンダーシティ店
-愛知県名古屋市西区二方町40番</t>
+          <t>株式会社愛知イエローハット　一宮店
+一宮市緑４－３ー１３</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>19.1km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>7/28(火)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>江南中央食品
-江南市古知野町北屋敷242</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>1-5-8　1-5-29　1-5-37</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>6.1km</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>サロンド榮
+一宮市浅野西大土106</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>大口屋木賀工場
-江南市木賀町定和244-1 その他</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>九品寺幼稚園
+一宮市真清田2-14-7</t>
         </is>
       </c>
     </row>
@@ -1596,17 +1585,17 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -1621,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1651,7 +1640,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室6で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計9名（教室6で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -1681,77 +1670,87 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>7/29(水)</t>
+          <t>7/31(金)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>榮美容室本店
-一宮市大江2-9-16</t>
+          <t>江南市立布袋北保育園
+江南市安良町八王子137</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-27</t>
+          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>17.3km</t>
+          <t>18.0km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>7/30(木)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園
-江南市高屋町大師７２番地</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>14.9km</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>江南市立古知野南保育園
+江南市古知野町塔塚160</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>江南市立小鹿保育園
-江南市小杁町長者毛東1</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>九品寺幼稚園
+一宮市真清田2-14-7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
+      </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>リスパック株式会社 真空成形工場
-愛知県犬山市羽黒宮浦1番地</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+          <t>きもの館なかね
+愛知県江南市古知野町本郷３４</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>8.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>江南市立門弟山保育園
+江南市村久野町門弟山271</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>江南市立古知野西保育園
+江南市東野町郷前48</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
@@ -1759,19 +1758,28 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
     </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="23" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="23" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A7:A9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1844,62 +1852,62 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>8/26(水)</t>
+          <t>7/31(金)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>株式会社デンケン
-愛知県犬山市大字羽黒字馬道7番地1</t>
+          <t>福玉ロジスティクス株式会社　大口センター
+集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-1-25　2-4-28</t>
+          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>15.5km</t>
+          <t>9.2km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>8/27(木)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>株式会社林商店
-愛知県江南市野白町東千丸88</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>2-4-15　2-4-19　2-1-30　2-2-19　2-3-14　2-4-16</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>20.5km</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>株式会社メイコン　本社
+本社（愛知県小牧市大字三ツ渕950番地）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>江南市立宮田保育園
-江南市飛保町新開23</t>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>福玉米粒麦株式会社
+愛知県江南市南山町西31</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-1-22　2-2-1　2-2-12</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>5.7km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>株式会社デンケン
-愛知県犬山市大字羽黒字馬道7番地1</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>江南市立布袋保育園
+江南市布袋下山町南70</t>
         </is>
       </c>
     </row>
@@ -1923,16 +1931,19 @@
       <c r="A14" s="23" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -1947,7 +1958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2007,74 +2018,79 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>8/25(火)</t>
+          <t>7/31(金)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>株式会社愛知イエローハット　一宮店
-一宮市緑４－３ー１３</t>
+          <t>東罐興業株式会社　小牧工場
+愛知県小牧市東田中2118</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-2-2　2-2-18　2-1-10　2-1-31</t>
+          <t>1-5-34　2-3-8　2-3-13</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>27.0km</t>
+          <t>22.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>TJ天気予報 7mm 北名古屋店
-北名古屋市鹿田才海82番2</t>
+          <t>東名化学工業株式会社　小牧工場
+小牧市大草檀之上5410</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>8/26(水)</t>
+          <t>8/24(月)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>アメーテールアーム
-愛知県小牧市市之久田1-73-1</t>
+          <t>美容室ISA
+丹羽郡大口町丸2-36 メガドンキユニー大口店　1F</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2-1-12　2-4-10　2-3-5　2-3-19　2-4-17</t>
+          <t>2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>38.7km</t>
+          <t>9.9km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>アイカテック建材株式会社名古屋工場
-愛知県海部郡大治町大字西條字西之川２５</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+          <t>江南市立古知野東保育園
+江南市高屋町大師７２番地</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>江南市立小鹿保育園
+江南市小杁町長者毛東1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -2084,20 +2100,23 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C8:C10"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
@@ -2173,70 +2192,70 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>8/25(火)</t>
+          <t>7/27(月)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>きもの館なかね
+愛知県江南市古知野町本郷３４</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>1-5-9　1-5-10　1-5-26　1-5-30　1-5-40</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>14.1km</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>江南市立宮田南保育園
 江南市前飛保町西町　2</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>2-1-18　2-4-6　2-1-2</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>9.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>江南市立宮田東保育園
-江南市宮田神明町栄174</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>8/26(水)</t>
-        </is>
-      </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>株式会社愛知イエローハット　一宮店
-一宮市緑４－３ー１３</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>19.1km</t>
+          <t>株式会社扶桑守口食品
+愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>サロンド榮
-一宮市浅野西大土106</t>
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>7/28(火)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>江南市立藤里保育園
+江南市藤が丘7丁目1-16</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2-2-13　2-1-15　2-4-20</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>28.7km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>九品寺幼稚園
-一宮市真清田2-14-7</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>東名化学工業株式会社　小牧工場
+小牧市大草檀之上5410</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2281,17 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -2287,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2347,79 +2366,74 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>8/26(水)</t>
+          <t>8/25(火)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>株式会社綿半ホームエイド江南店
-江南市上奈良町緑13</t>
+          <t>株式会社愛知イエローハット　一宮店
+一宮市緑４－３ー１３</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-1-9　2-1-20　2-1-24　2-2-10</t>
+          <t>2-2-2　2-2-18　2-1-10　2-1-31</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>8.6km</t>
+          <t>27.0km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立布袋東保育園
-江南市小折町八反畑１４７</t>
+          <t>TJ天気予報 7mm 北名古屋店
+北名古屋市鹿田才海82番2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>8/27(木)</t>
+          <t>8/26(水)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>江南市立布袋東保育園
-江南市小折町八反畑１４７</t>
+          <t>アメーテールアーム
+愛知県小牧市市之久田1-73-1</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2-3-6　2-4-23　2-2-16　2-3-7　2-2-17</t>
+          <t>2-1-12　2-4-10　2-3-5　2-3-19　2-4-17</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>18.3km</t>
+          <t>38.7km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>株式会社愛知イエローハット　一宮店
-一宮市緑４－３ー１３</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>FUSION
-一宮市大江2-9-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+          <t>アイカテック建材株式会社名古屋工場
+愛知県海部郡大治町大字西條字西之川２５</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -2429,23 +2443,20 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="D8:D10"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
@@ -2491,7 +2502,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計8名（教室8で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計9名（教室8で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -2521,70 +2532,70 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>7/27(月)</t>
+          <t>8/26(水)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>きもの館なかね
-愛知県江南市古知野町本郷３４</t>
+          <t>株式会社綿半ホームエイド江南店
+江南市上奈良町緑13</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-9　1-5-10　1-5-26　1-5-30　1-5-40</t>
+          <t>2-1-9　2-1-20　2-1-24　2-2-10</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>14.1km</t>
+          <t>8.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立宮田南保育園
-江南市前飛保町西町　2</t>
+          <t>江南市立布袋東保育園
+江南市小折町八反畑１４７</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
+      </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>株式会社扶桑守口食品
-愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
+          <t>江南市立布袋東保育園
+江南市小折町八反畑１４７</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-3-6　2-4-23　2-2-16　2-3-7　2-2-17</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>18.3km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>7/28(火)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>江南市立藤里保育園
-江南市藤が丘7丁目1-16</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>2-2-13　2-1-15　2-4-20</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>28.7km</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>株式会社愛知イエローハット　一宮店
+一宮市緑４－３ー１３</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>東名化学工業株式会社　小牧工場
-小牧市大草檀之上5410</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>FUSION
+一宮市大江2-9-19</t>
         </is>
       </c>
     </row>
@@ -2610,17 +2621,17 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -2665,7 +2676,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計15名（教室1で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計16名（教室1で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -2700,34 +2711,34 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>福玉ロジスティクス株式会社　大口センター
-集合場所：丹羽郡大口町御供所1-65　就業体験場所：丹羽郡大口町御供所3丁目122番地</t>
+          <t>江南市立古知野東保育園
+江南市高屋町大師７２番地</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-3-8　2-3-13</t>
+          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>26.1km</t>
+          <t>8.4km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>株式会社メイコン　本社
-本社（愛知県小牧市大字三ツ渕950番地）</t>
+          <t>グンゼ江南工場
+愛知県江南市村久野町鳥附１番地</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>東名化学工業株式会社　小牧工場
-小牧市大草檀之上5410</t>
+          <t>江南市立宮田東保育園
+江南市宮田神明町栄174</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2979,7 +2990,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計12名（教室2で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室2で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3020,7 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>7/29(水)</t>
+          <t>7/27(月)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -3020,63 +3031,68 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-2-14　2-4-21　2-1-1　2-1-19　2-4-14</t>
+          <t>1-5-17　2-1-11　1-5-20　1-5-21</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>10.3km</t>
+          <t>5.8km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>キムラユニティー株式会社　犬山工場
-愛知県犬山市字舟田10番地</t>
+          <t>大口屋木賀工場
+江南市木賀町定和244-1 その他</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>7/31(金)</t>
+          <t>7/28(火)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>グンゼ江南工場
-愛知県江南市村久野町鳥附１番地</t>
+          <t>サンハウス食品株式会社
+愛知県江南市高屋町西里７７番地</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
+          <t>1-5-16　1-5-19　1-5-12　1-5-14　1-5-7　1-5-15</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>8.3km</t>
+          <t>11.0km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>江南市立宮田東保育園
-江南市宮田神明町栄174</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+          <t>江南市立草井保育園
+江南市草井町若草57</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>株式会社扶桑守口食品
+愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -3086,20 +3102,23 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C8:C10"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
@@ -3115,7 +3134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3175,71 +3194,66 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>7/31(金)</t>
+          <t>7/29(水)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園
-江南市高屋町大師７２番地</t>
+          <t>株式会社青山製作所　大口工場
+愛知県丹羽郡大口町高橋一丁目8番地</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-4-22</t>
+          <t>2-2-14　2-4-21　2-1-1　2-1-19　2-4-14</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>3.2km</t>
+          <t>10.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>8/24(月)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>きもの館なかね
-愛知県江南市古知野町本郷３４</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>8.5km</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>キムラユニティー株式会社　犬山工場
+愛知県犬山市字舟田10番地</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>江南市立門弟山保育園
-江南市村久野町門弟山271</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>江南市立古知野西保育園
-江南市東野町郷前48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>7/30(木)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>江南市立藤里保育園
+江南市藤が丘7丁目1-16</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-4-7</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>7.2km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="23" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="23" t="inlineStr"/>
@@ -3249,23 +3263,20 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D7:D9"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -3338,70 +3349,70 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>7/27(月)</t>
+          <t>7/29(水)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>株式会社青山製作所　大口工場
-愛知県丹羽郡大口町高橋一丁目8番地</t>
+          <t>株式会社綿半ホームエイド江南店
+江南市上奈良町緑13</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-17　2-1-11　1-5-20　1-5-21</t>
+          <t>2-1-21　2-2-4　2-2-20</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>5.8km</t>
+          <t>8.6km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>大口屋木賀工場
-江南市木賀町定和244-1 その他</t>
+          <t>江南市立藤里保育園
+江南市藤が丘7丁目1-16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>7/28(火)</t>
+          <t>7/30(木)</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>サンハウス食品株式会社
-愛知県江南市高屋町西里７７番地</t>
+          <t>江南市立古知野中保育園
+江南市古知野町熱田203</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1-5-16　1-5-19　1-5-12　1-5-14　1-5-7　1-5-15</t>
+          <t>1-5-18　1-5-39　2-4-3　1-5-2　1-5-32　1-5-33　1-5-38</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>11.0km</t>
+          <t>9.7km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>江南市立草井保育園
-江南市草井町若草57</t>
+          <t>江南市立古知野西保育園
+江南市東野町郷前48</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>株式会社扶桑守口食品
-愛知県丹羽郡扶桑町大字山那字屋敷地757</t>
+          <t>ガレ・ドゥ・ワタナベ
+江南市小折町八反畑8</t>
         </is>
       </c>
     </row>
@@ -3452,169 +3463,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>教室3　事前指導（7/17 4限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>担当教員</t>
-        </is>
-      </c>
-      <c r="B2" s="17">
-        <f>'7-17教室割当一覧'!C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計7名（教室3で他1名と同室）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>巡回日</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>訪問先企業</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>担当生徒</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>距離</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>7/31(金)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>東罐興業株式会社　小牧工場
-愛知県小牧市東田中2118</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>1-5-34</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>12.8km</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>8/24(月)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>美容室ISA
-丹羽郡大口町丸2-36 メガドンキユニー大口店　1F</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>9.9km</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園
-江南市高屋町大師７２番地</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>江南市立小鹿保育園
-江南市小杁町長者毛東1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>備考・メモ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="23" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3627,7 +3475,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>教室4　事前指導（7/17 4限）</t>
+          <t>教室3　事前指導（7/17 4限）</t>
         </is>
       </c>
     </row>
@@ -3638,14 +3486,14 @@
         </is>
       </c>
       <c r="B2" s="17">
-        <f>'7-17教室割当一覧'!C9</f>
+        <f>'7-17教室割当一覧'!C8</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室4で他1名と同室）</t>
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計7名（教室3で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -3673,72 +3521,72 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>7/29(水)</t>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>7/27(月)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ドコモショップ江南店
+愛知県江南市木賀町定和163</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>2-1-6　2-1-13　2-1-36　2-4-1</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>32.1km</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>江南市立藤里保育園
+江南市藤が丘7丁目1-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>GARN（ガルン）　モゾワンダーシティ店
+愛知県名古屋市西区二方町40番</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>7/28(火)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>江南中央食品
 江南市古知野町北屋敷242</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>7.7km</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>江南市立布袋西保育園
-江南市木賀町定和３１</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>ガレ・ドゥ・ワタナベ
-江南市小折町八反畑8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>7/30(木)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>江南市立藤里保育園
-江南市藤が丘7丁目1-16</t>
-        </is>
-      </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>2-4-7　2-2-9　2-2-11　2-2-15　2-4-12</t>
+          <t>1-5-8　1-5-29　1-5-37</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>45.9km</t>
+          <t>6.1km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店
-愛知県名古屋市中村区並木1-81-1</t>
+          <t>大口屋木賀工場
+江南市木賀町定和244-1 その他</t>
         </is>
       </c>
     </row>
@@ -3783,13 +3631,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3812,14 +3660,14 @@
         </is>
       </c>
       <c r="B2" s="17">
-        <f>'7-17教室割当一覧'!C10</f>
+        <f>'7-17教室割当一覧'!C9</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計7名（教室4で他1名と同室）</t>
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室4で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -3847,81 +3695,76 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>7/31(金)</t>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>7/29(水)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>江南市立布袋北保育園
-江南市安良町八王子137</t>
+          <t>榮美容室本店
+一宮市大江2-9-16</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
+          <t>1-5-27</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>18.0km</t>
+          <t>17.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>江南市立古知野南保育園
-江南市古知野町塔塚160</t>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>7/30(木)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>江南市立古知野東保育園
+江南市高屋町大師７２番地</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>1-5-3　1-5-31　1-5-36　2-2-8　1-5-6　2-1-27　2-1-28　2-3-11　2-3-17</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>14.9km</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>九品寺幼稚園
-一宮市真清田2-14-7</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>江南市立小鹿保育園
+江南市小杁町長者毛東1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>8/24(月)</t>
-        </is>
-      </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>福玉米粒麦株式会社
-愛知県江南市南山町西31</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>2-1-22　2-2-1　2-2-12</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>5.7km</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>江南市立布袋保育園
-江南市布袋下山町南70</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+          <t>リスパック株式会社 真空成形工場
+愛知県犬山市羽黒宮浦1番地</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -3932,23 +3775,180 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="A7:A9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="D7:D9"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>教室4　事前指導（7/17 4限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>担当教員</t>
+        </is>
+      </c>
+      <c r="B2" s="17">
+        <f>'7-17教室割当一覧'!C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計8名（教室4で他1名と同室）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>巡回日</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>訪問先企業</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>担当生徒</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>距離</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>株式会社デンケン
+愛知県犬山市大字羽黒字馬道7番地1</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>2-1-25　2-4-28</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>15.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>株式会社林商店
+愛知県江南市野白町東千丸88</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>2-4-15　2-4-19　2-1-30　2-2-19　2-3-14　2-4-16</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>20.5km</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>江南市立宮田保育園
+江南市飛保町新開23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>株式会社デンケン
+愛知県犬山市大字羽黒字馬道7番地1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>備考・メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="23" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="23" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="23" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="23" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>

--- a/7-17事前指導_教室割当.xlsx
+++ b/7-17事前指導_教室割当.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="7-17教室割当一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="教員8_詳細" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="教員16_詳細" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="教員2_詳細" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="教員5_詳細" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="教員6_詳細" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="教員3_詳細" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="教員7_詳細" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="教員15_詳細" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="教員4_詳細" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="教員13_詳細" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="教員10_詳細" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="教員9_詳細" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="教員11_詳細" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="教員1_詳細" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="教員12_詳細" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="教員14_詳細" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-17教室割当一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員8_詳細" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員16_詳細" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員2_詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員5_詳細" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員6_詳細" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員3_詳細" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員7_詳細" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員15_詳細" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員11_詳細" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員13_詳細" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員4_詳細" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員9_詳細" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員10_詳細" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員1_詳細" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員12_詳細" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教員14_詳細" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -676,7 +676,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7月17日(金) 4限　インターンシップ事前指導　教室割当表（教員15名体制）</t>
+          <t>7月17日(金) 4限　インターンシップ事前指導　教室割当表（教員16名体制）</t>
         </is>
       </c>
     </row>
@@ -743,22 +743,22 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>7/31(金): 江南市立古知野東保育園 → グンゼ江南工場 → 江南市立宮田東保育園
+          <t>7/31(金): グンゼ江南工場 → 江南市立宮田東保育園
 8/25(火): 株式会社青山製作所　大口工場 → 株式会社東海理化電機製作所 → 江南郵便局</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25　2-3-10　2-4-13　2-1-34　2-1-35　2-4-29　2-1-7　2-2-3　2-2-5</t>
+          <t>1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25　2-3-10　2-4-13　2-1-34　2-1-35　2-4-29　2-1-7　2-2-3　2-2-5</t>
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
           <t>計
-21名</t>
+20名</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>教員4</t>
+          <t>教員11</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
@@ -1002,143 +1002,143 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
+          <t>7/31(金): 東罐興業株式会社　小牧工場 → 東名化学工業株式会社　小牧工場
+8/24(月): 美容室ISA → 江南市立古知野東保育園 → 江南市立小鹿保育園</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>1-5-34　2-3-8　2-3-13　2-1-33　2-3-18　2-4-5　2-4-22　2-4-26　2-3-1　2-4-27</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>計
+18名</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>教員13</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>8/25(火): 江南市立宮田南保育園 → 江南市立宮田東保育園
+8/26(水): 株式会社愛知イエローハット　一宮店 → サロンド榮 → 九品寺幼稚園</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>2-1-18　2-4-6　2-1-2　2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>教室6</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>教員4</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
           <t>7/29(水): 江南中央食品 → 江南市立布袋西保育園 → ガレ・ドゥ・ワタナベ
 7/30(木): ＮＸキャッシュ・ロジスティクス株式会社　中部支店</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13　2-2-9　2-2-11　2-2-15　2-4-12</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>計
 17名</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>教員13</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
+    <row r="14" ht="50" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>教員9</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>8/25(火): 江南市立宮田南保育園 → 江南市立宮田東保育園
-8/26(水): 株式会社愛知イエローハット　一宮店 → サロンド榮 → 九品寺幼稚園</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>2-1-18　2-4-6　2-1-2　2-2-7　2-3-16　2-1-26　2-1-8　2-4-9</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="n">
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>7/31(金): 福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社
+8/24(月): 福玉米粒麦株式会社 → 江南市立布袋保育園</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-1-22　2-2-1　2-2-12</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>教室6</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>教室7</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>教員10</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>2日</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>7/31(金): 江南市立布袋北保育園 → 江南市立古知野南保育園 → 九品寺幼稚園
 8/24(月): きもの館なかね → 江南市立門弟山保育園 → 江南市立古知野西保育園</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>1-5-28　1-5-23　2-1-17　1-5-5　2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>計
-17名</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>教員9</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>7/31(金): 福玉ロジスティクス株式会社　大口センター → 株式会社メイコン　本社
-8/24(月): 福玉米粒麦株式会社 → 江南市立布袋保育園</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>2-4-18　2-4-25　2-1-14　2-2-6　2-4-24　2-1-22　2-2-1　2-2-12</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>教室7</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>教員11</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>2日</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>7/31(金): 東罐興業株式会社　小牧工場 → 東名化学工業株式会社　小牧工場
-8/24(月): 美容室ISA → 江南市立古知野東保育園 → 江南市立小鹿保育園</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>1-5-34　2-3-8　2-3-13　2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
         </is>
       </c>
       <c r="G15" s="9" t="n">
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1303,7 +1303,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計9名（教室5で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計10名（教室5で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -1333,74 +1333,79 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>7/29(水)</t>
+          <t>7/31(金)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>江南中央食品
-江南市古知野町北屋敷242</t>
+          <t>東罐興業株式会社　小牧工場
+愛知県小牧市東田中2118</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13</t>
+          <t>1-5-34　2-3-8　2-3-13</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>7.7km</t>
+          <t>22.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立布袋西保育園
-江南市木賀町定和３１</t>
+          <t>東名化学工業株式会社　小牧工場
+小牧市大草檀之上5410</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
+      </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ガレ・ドゥ・ワタナベ
-江南市小折町八反畑8</t>
+          <t>美容室ISA
+丹羽郡大口町丸2-36 メガドンキユニー大口店　1F</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>2-1-33　2-3-18　2-4-5　2-4-22　2-4-26　2-3-1　2-4-27</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>9.9km</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>7/30(木)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店
-愛知県名古屋市中村区並木1-81-1</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>2-2-9　2-2-11　2-2-15　2-4-12</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>40.6km</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>江南市立古知野東保育園
+江南市高屋町大師７２番地</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>江南市立小鹿保育園
+江南市小杁町長者毛東1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="23" t="inlineStr"/>
@@ -1411,17 +1416,23 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
     </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="23" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -1610,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1670,87 +1681,77 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>7/31(金)</t>
+          <t>7/29(水)</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>江南市立布袋北保育園
-江南市安良町八王子137</t>
+          <t>江南中央食品
+江南市古知野町北屋敷242</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
+          <t>1-5-35　1-5-4　1-5-22　1-5-11　1-5-13</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>18.0km</t>
+          <t>7.7km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>江南市立古知野南保育園
-江南市古知野町塔塚160</t>
+          <t>江南市立布袋西保育園
+江南市木賀町定和３１</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>九品寺幼稚園
-一宮市真清田2-14-7</t>
+          <t>ガレ・ドゥ・ワタナベ
+江南市小折町八反畑8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>8/24(月)</t>
+          <t>7/30(木)</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>きもの館なかね
-愛知県江南市古知野町本郷３４</t>
+          <t>ＮＸキャッシュ・ロジスティクス株式会社　中部支店
+愛知県名古屋市中村区並木1-81-1</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
+          <t>2-2-9　2-2-11　2-2-15　2-4-12</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>8.5km</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>江南市立門弟山保育園
-江南市村久野町門弟山271</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>江南市立古知野西保育園
-江南市東野町郷前48</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+          <t>40.6km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="23" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
@@ -1758,28 +1759,19 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="23" t="inlineStr"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="23" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1958,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2023,77 +2015,82 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>東罐興業株式会社　小牧工場
-愛知県小牧市東田中2118</t>
+          <t>江南市立布袋北保育園
+江南市安良町八王子137</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1-5-34　2-3-8　2-3-13</t>
+          <t>1-5-28　1-5-23　2-1-17　1-5-5</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>22.3km</t>
+          <t>18.0km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>東名化学工業株式会社　小牧工場
-小牧市大草檀之上5410</t>
+          <t>江南市立古知野南保育園
+江南市古知野町塔塚160</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>九品寺幼稚園
+一宮市真清田2-14-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>8/24(月)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>美容室ISA
-丹羽郡大口町丸2-36 メガドンキユニー大口店　1F</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>2-1-33　2-3-18　2-4-5　2-4-26　2-3-1　2-4-27</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>9.9km</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>江南市立古知野東保育園
-江南市高屋町大師７２番地</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>きもの館なかね
+愛知県江南市古知野町本郷３４</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2-4-2　2-4-4　2-1-3　2-3-3　2-4-8</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>8.5km</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>江南市立小鹿保育園
-江南市小杁町長者毛東1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>江南市立門弟山保育園
+江南市村久野町門弟山271</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>江南市立古知野西保育園
+江南市東野町郷前48</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
@@ -2103,23 +2100,26 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="23" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
+    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2646,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2676,7 +2676,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計16名（教室1で他1名と同室）</t>
+          <t>夏休み中の巡回予定：2日間 ／ 対象生徒 計15名（教室1で他1名と同室）</t>
         </is>
       </c>
     </row>
@@ -2711,82 +2711,77 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>江南市立古知野東保育園
-江南市高屋町大師７２番地</t>
+          <t>グンゼ江南工場
+愛知県江南市村久野町鳥附１番地</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2-4-22　1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
+          <t>1-5-24　2-1-29　2-1-32　2-3-12　2-3-15　1-5-1　1-5-25</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>8.4km</t>
+          <t>8.3km</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>グンゼ江南工場
-愛知県江南市村久野町鳥附１番地</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
           <t>江南市立宮田東保育園
 江南市宮田神明町栄174</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>8/25(火)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>株式会社青山製作所　大口工場
 愛知県丹羽郡大口町高橋一丁目8番地</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2-3-10　2-4-13　2-1-34　2-1-35　2-4-29　2-1-7　2-2-3　2-2-5</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>8.7km</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>株式会社東海理化電機製作所
 愛知県丹羽郡大口町豊田三丁目260番地</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>江南郵便局
 江南市赤童子町良原143-1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>備考・メモ</t>
         </is>
       </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="23" t="inlineStr"/>
@@ -2796,26 +2791,23 @@
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A9:A11"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
